--- a/SGC-CKN/Excel/17c9b475-1132-4ca3-a14e-20fbe05ee07c_Thanh_Hoá_P1-51_D800_05-04-2026.xlsx
+++ b/SGC-CKN/Excel/17c9b475-1132-4ca3-a14e-20fbe05ee07c_Thanh_Hoá_P1-51_D800_05-04-2026.xlsx
@@ -326,17 +326,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFF7ED"/>
+        <fgColor rgb="FFD1FAE5"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFDE68A"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD1FAE5"/>
       </patternFill>
     </fill>
     <fill>
@@ -367,6 +362,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFA5F3FC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFF7ED"/>
       </patternFill>
     </fill>
     <fill>
@@ -497,62 +497,62 @@
     <xf numFmtId="0" fontId="6" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="11" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="11" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="11" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="11" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="11" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="11" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="12" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="12" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="12" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="12" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="12" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="12" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="13" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="13" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="13" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="13" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="13" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="13" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="14" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="14" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="14" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="14" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1146,19 +1146,19 @@
         <v>28</v>
       </c>
       <c r="F11" s="5">
-        <v>-0.71</v>
+        <v>0</v>
       </c>
       <c r="G11" s="5">
-        <v>-0.6</v>
+        <v>-3.7</v>
       </c>
       <c r="H11" s="5">
         <v>0.08</v>
       </c>
       <c r="I11" s="5">
-        <v>0.11</v>
+        <v>3.7</v>
       </c>
       <c r="J11" s="8">
-        <v>1.32</v>
+        <v>44.4</v>
       </c>
       <c r="K11" s="6" t="s">
         <v>29</v>
@@ -1181,231 +1181,231 @@
         <v>32</v>
       </c>
       <c r="F12" s="9">
-        <v>-0.6</v>
+        <v>-3.7</v>
       </c>
       <c r="G12" s="9">
-        <v>-5.7</v>
+        <v>-7</v>
       </c>
       <c r="H12" s="9">
         <v>0.17</v>
       </c>
       <c r="I12" s="9">
-        <v>5.1</v>
-      </c>
-      <c r="J12" s="12">
-        <v>30.6</v>
+        <v>3.3</v>
+      </c>
+      <c r="J12" s="8">
+        <v>19.8</v>
       </c>
       <c r="K12" s="10" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="13" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A13" s="13" t="s">
+      <c r="A13" s="12" t="s">
         <v>33</v>
       </c>
-      <c r="B13" s="13" t="s">
+      <c r="B13" s="12" t="s">
         <v>11</v>
       </c>
-      <c r="C13" s="14" t="s">
+      <c r="C13" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="D13" s="15" t="s">
+      <c r="D13" s="14" t="s">
         <v>32</v>
       </c>
-      <c r="E13" s="15" t="s">
+      <c r="E13" s="14" t="s">
         <v>35</v>
       </c>
-      <c r="F13" s="13">
-        <v>-5.7</v>
-      </c>
-      <c r="G13" s="13">
+      <c r="F13" s="12">
+        <v>-7</v>
+      </c>
+      <c r="G13" s="12">
         <v>-15.8</v>
       </c>
-      <c r="H13" s="13">
+      <c r="H13" s="12">
         <v>0.83</v>
       </c>
-      <c r="I13" s="13">
-        <v>10.1</v>
-      </c>
-      <c r="J13" s="12">
-        <v>12.12</v>
-      </c>
-      <c r="K13" s="14" t="s">
+      <c r="I13" s="12">
+        <v>8.8</v>
+      </c>
+      <c r="J13" s="8">
+        <v>10.56</v>
+      </c>
+      <c r="K13" s="13" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="14" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A14" s="16" t="s">
+      <c r="A14" s="15" t="s">
         <v>36</v>
       </c>
-      <c r="B14" s="16" t="s">
+      <c r="B14" s="15" t="s">
         <v>11</v>
       </c>
-      <c r="C14" s="17" t="s">
+      <c r="C14" s="16" t="s">
         <v>37</v>
       </c>
-      <c r="D14" s="18" t="s">
+      <c r="D14" s="17" t="s">
         <v>35</v>
       </c>
-      <c r="E14" s="18" t="s">
+      <c r="E14" s="17" t="s">
         <v>38</v>
       </c>
-      <c r="F14" s="16">
+      <c r="F14" s="15">
         <v>-15.8</v>
       </c>
-      <c r="G14" s="16">
+      <c r="G14" s="15">
         <v>-21</v>
       </c>
-      <c r="H14" s="16">
+      <c r="H14" s="15">
         <v>0.33</v>
       </c>
-      <c r="I14" s="16">
+      <c r="I14" s="15">
         <v>5.2</v>
       </c>
-      <c r="J14" s="12">
+      <c r="J14" s="8">
         <v>15.6</v>
       </c>
-      <c r="K14" s="17" t="s">
+      <c r="K14" s="16" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="15" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A15" s="19" t="s">
+      <c r="A15" s="18" t="s">
         <v>39</v>
       </c>
-      <c r="B15" s="19" t="s">
+      <c r="B15" s="18" t="s">
         <v>11</v>
       </c>
-      <c r="C15" s="20" t="s">
+      <c r="C15" s="19" t="s">
         <v>40</v>
       </c>
-      <c r="D15" s="21" t="s">
+      <c r="D15" s="20" t="s">
         <v>38</v>
       </c>
-      <c r="E15" s="21" t="s">
+      <c r="E15" s="20" t="s">
         <v>41</v>
       </c>
-      <c r="F15" s="19">
+      <c r="F15" s="18">
         <v>-21</v>
       </c>
-      <c r="G15" s="19">
+      <c r="G15" s="18">
         <v>-25</v>
       </c>
-      <c r="H15" s="19">
+      <c r="H15" s="18">
         <v>0.5</v>
       </c>
-      <c r="I15" s="19">
+      <c r="I15" s="18">
         <v>4</v>
       </c>
-      <c r="J15" s="12">
+      <c r="J15" s="8">
         <v>8</v>
       </c>
-      <c r="K15" s="20" t="s">
+      <c r="K15" s="19" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="16" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A16" s="22" t="s">
+      <c r="A16" s="21" t="s">
         <v>42</v>
       </c>
-      <c r="B16" s="22" t="s">
+      <c r="B16" s="21" t="s">
         <v>11</v>
       </c>
-      <c r="C16" s="23" t="s">
+      <c r="C16" s="22" t="s">
         <v>43</v>
       </c>
-      <c r="D16" s="24" t="s">
+      <c r="D16" s="23" t="s">
         <v>44</v>
       </c>
-      <c r="E16" s="24" t="s">
+      <c r="E16" s="23" t="s">
         <v>45</v>
       </c>
-      <c r="F16" s="22">
+      <c r="F16" s="21">
         <v>-25</v>
       </c>
-      <c r="G16" s="22">
+      <c r="G16" s="21">
         <v>-29</v>
       </c>
-      <c r="H16" s="22">
+      <c r="H16" s="21">
         <v>0.33</v>
       </c>
-      <c r="I16" s="22">
+      <c r="I16" s="21">
         <v>4</v>
       </c>
-      <c r="J16" s="12">
+      <c r="J16" s="8">
         <v>12</v>
       </c>
-      <c r="K16" s="23" t="s">
+      <c r="K16" s="22" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="17" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A17" s="25" t="s">
+      <c r="A17" s="24" t="s">
         <v>46</v>
       </c>
-      <c r="B17" s="25" t="s">
+      <c r="B17" s="24" t="s">
         <v>11</v>
       </c>
-      <c r="C17" s="26" t="s">
+      <c r="C17" s="25" t="s">
         <v>47</v>
       </c>
-      <c r="D17" s="27" t="s">
+      <c r="D17" s="26" t="s">
         <v>45</v>
       </c>
-      <c r="E17" s="27" t="s">
+      <c r="E17" s="26" t="s">
         <v>48</v>
       </c>
-      <c r="F17" s="25">
+      <c r="F17" s="24">
         <v>-29</v>
       </c>
-      <c r="G17" s="25">
+      <c r="G17" s="24">
         <v>-39.5</v>
       </c>
-      <c r="H17" s="25">
+      <c r="H17" s="24">
         <v>1.27</v>
       </c>
-      <c r="I17" s="25">
+      <c r="I17" s="24">
         <v>10.5</v>
       </c>
-      <c r="J17" s="12">
+      <c r="J17" s="8">
         <v>8.29</v>
       </c>
-      <c r="K17" s="26" t="s">
+      <c r="K17" s="25" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="18" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A18" s="28" t="s">
+      <c r="A18" s="27" t="s">
         <v>49</v>
       </c>
-      <c r="B18" s="28" t="s">
+      <c r="B18" s="27" t="s">
         <v>11</v>
       </c>
-      <c r="C18" s="29" t="s">
+      <c r="C18" s="28" t="s">
         <v>50</v>
       </c>
-      <c r="D18" s="30" t="s">
+      <c r="D18" s="29" t="s">
         <v>48</v>
       </c>
-      <c r="E18" s="30" t="s">
+      <c r="E18" s="29" t="s">
         <v>51</v>
       </c>
-      <c r="F18" s="28">
+      <c r="F18" s="27">
         <v>-39.5</v>
       </c>
-      <c r="G18" s="28">
+      <c r="G18" s="27">
         <v>-44.43</v>
       </c>
-      <c r="H18" s="28">
+      <c r="H18" s="27">
         <v>1.5</v>
       </c>
-      <c r="I18" s="28">
+      <c r="I18" s="27">
         <v>4.93</v>
       </c>
-      <c r="J18" s="8">
+      <c r="J18" s="30">
         <v>3.29</v>
       </c>
-      <c r="K18" s="29" t="s">
+      <c r="K18" s="28" t="s">
         <v>29</v>
       </c>
     </row>
@@ -1558,19 +1558,19 @@
         <v>1</v>
       </c>
       <c r="E2" s="5">
-        <v>-0.71</v>
+        <v>0</v>
       </c>
       <c r="F2" s="5">
-        <v>-0.6</v>
+        <v>-3.7</v>
       </c>
       <c r="G2" s="5">
         <v>0.08</v>
       </c>
       <c r="H2" s="5">
-        <v>0.11</v>
+        <v>3.7</v>
       </c>
       <c r="I2" s="8">
-        <v>1.32</v>
+        <v>44.4</v>
       </c>
     </row>
     <row r="3" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1587,192 +1587,192 @@
         <v>1</v>
       </c>
       <c r="E3" s="9">
-        <v>-0.6</v>
+        <v>-3.7</v>
       </c>
       <c r="F3" s="9">
-        <v>-5.7</v>
+        <v>-7</v>
       </c>
       <c r="G3" s="9">
         <v>0.17</v>
       </c>
       <c r="H3" s="9">
-        <v>5.1</v>
-      </c>
-      <c r="I3" s="12">
-        <v>30.6</v>
+        <v>3.3</v>
+      </c>
+      <c r="I3" s="8">
+        <v>19.8</v>
       </c>
     </row>
     <row r="4" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A4" s="13">
+      <c r="A4" s="12">
         <v>3</v>
       </c>
-      <c r="B4" s="13" t="s">
+      <c r="B4" s="12" t="s">
         <v>11</v>
       </c>
-      <c r="C4" s="14" t="s">
+      <c r="C4" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="D4" s="13">
+      <c r="D4" s="12">
         <v>1</v>
       </c>
-      <c r="E4" s="13">
-        <v>-5.7</v>
-      </c>
-      <c r="F4" s="13">
+      <c r="E4" s="12">
+        <v>-7</v>
+      </c>
+      <c r="F4" s="12">
         <v>-15.8</v>
       </c>
-      <c r="G4" s="13">
+      <c r="G4" s="12">
         <v>0.83</v>
       </c>
-      <c r="H4" s="13">
-        <v>10.1</v>
-      </c>
-      <c r="I4" s="12">
-        <v>12.12</v>
+      <c r="H4" s="12">
+        <v>8.8</v>
+      </c>
+      <c r="I4" s="8">
+        <v>10.56</v>
       </c>
     </row>
     <row r="5" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A5" s="16">
+      <c r="A5" s="15">
         <v>4</v>
       </c>
-      <c r="B5" s="16" t="s">
+      <c r="B5" s="15" t="s">
         <v>11</v>
       </c>
-      <c r="C5" s="17" t="s">
+      <c r="C5" s="16" t="s">
         <v>37</v>
       </c>
-      <c r="D5" s="16">
+      <c r="D5" s="15">
         <v>1</v>
       </c>
-      <c r="E5" s="16">
+      <c r="E5" s="15">
         <v>-15.8</v>
       </c>
-      <c r="F5" s="16">
+      <c r="F5" s="15">
         <v>-21</v>
       </c>
-      <c r="G5" s="16">
+      <c r="G5" s="15">
         <v>0.33</v>
       </c>
-      <c r="H5" s="16">
+      <c r="H5" s="15">
         <v>5.2</v>
       </c>
-      <c r="I5" s="12">
+      <c r="I5" s="8">
         <v>15.6</v>
       </c>
     </row>
     <row r="6" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A6" s="19">
+      <c r="A6" s="18">
         <v>5</v>
       </c>
-      <c r="B6" s="19" t="s">
+      <c r="B6" s="18" t="s">
         <v>11</v>
       </c>
-      <c r="C6" s="20" t="s">
+      <c r="C6" s="19" t="s">
         <v>40</v>
       </c>
-      <c r="D6" s="19">
+      <c r="D6" s="18">
         <v>1</v>
       </c>
-      <c r="E6" s="19">
+      <c r="E6" s="18">
         <v>-21</v>
       </c>
-      <c r="F6" s="19">
+      <c r="F6" s="18">
         <v>-25</v>
       </c>
-      <c r="G6" s="19">
+      <c r="G6" s="18">
         <v>0.5</v>
       </c>
-      <c r="H6" s="19">
+      <c r="H6" s="18">
         <v>4</v>
       </c>
-      <c r="I6" s="12">
+      <c r="I6" s="8">
         <v>8</v>
       </c>
     </row>
     <row r="7" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A7" s="22">
+      <c r="A7" s="21">
         <v>6</v>
       </c>
-      <c r="B7" s="22" t="s">
+      <c r="B7" s="21" t="s">
         <v>11</v>
       </c>
-      <c r="C7" s="23" t="s">
+      <c r="C7" s="22" t="s">
         <v>43</v>
       </c>
-      <c r="D7" s="22">
+      <c r="D7" s="21">
         <v>1</v>
       </c>
-      <c r="E7" s="22">
+      <c r="E7" s="21">
         <v>-25</v>
       </c>
-      <c r="F7" s="22">
+      <c r="F7" s="21">
         <v>-29</v>
       </c>
-      <c r="G7" s="22">
+      <c r="G7" s="21">
         <v>0.33</v>
       </c>
-      <c r="H7" s="22">
+      <c r="H7" s="21">
         <v>4</v>
       </c>
-      <c r="I7" s="12">
+      <c r="I7" s="8">
         <v>12</v>
       </c>
     </row>
     <row r="8" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A8" s="25">
+      <c r="A8" s="24">
         <v>7</v>
       </c>
-      <c r="B8" s="25" t="s">
+      <c r="B8" s="24" t="s">
         <v>11</v>
       </c>
-      <c r="C8" s="26" t="s">
+      <c r="C8" s="25" t="s">
         <v>47</v>
       </c>
-      <c r="D8" s="25">
+      <c r="D8" s="24">
         <v>1</v>
       </c>
-      <c r="E8" s="25">
+      <c r="E8" s="24">
         <v>-29</v>
       </c>
-      <c r="F8" s="25">
+      <c r="F8" s="24">
         <v>-39.5</v>
       </c>
-      <c r="G8" s="25">
+      <c r="G8" s="24">
         <v>1.27</v>
       </c>
-      <c r="H8" s="25">
+      <c r="H8" s="24">
         <v>10.5</v>
       </c>
-      <c r="I8" s="12">
+      <c r="I8" s="8">
         <v>8.29</v>
       </c>
     </row>
     <row r="9" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A9" s="28">
+      <c r="A9" s="27">
         <v>8</v>
       </c>
-      <c r="B9" s="28" t="s">
+      <c r="B9" s="27" t="s">
         <v>11</v>
       </c>
-      <c r="C9" s="29" t="s">
+      <c r="C9" s="28" t="s">
         <v>50</v>
       </c>
-      <c r="D9" s="28">
+      <c r="D9" s="27">
         <v>1</v>
       </c>
-      <c r="E9" s="28">
+      <c r="E9" s="27">
         <v>-39.5</v>
       </c>
-      <c r="F9" s="28">
+      <c r="F9" s="27">
         <v>-44.43</v>
       </c>
-      <c r="G9" s="28">
+      <c r="G9" s="27">
         <v>1.5</v>
       </c>
-      <c r="H9" s="28">
+      <c r="H9" s="27">
         <v>4.93</v>
       </c>
-      <c r="I9" s="8">
+      <c r="I9" s="30">
         <v>3.29</v>
       </c>
     </row>
@@ -1790,7 +1790,7 @@
         <v>8</v>
       </c>
       <c r="E10" s="33">
-        <v>-0.71</v>
+        <v>0</v>
       </c>
       <c r="F10" s="33">
         <v>-44.43</v>
@@ -1799,10 +1799,10 @@
         <v>5.02</v>
       </c>
       <c r="H10" s="33">
-        <v>43.94</v>
+        <v>44.43</v>
       </c>
       <c r="I10" s="33">
-        <v>8.76</v>
+        <v>8.86</v>
       </c>
     </row>
   </sheetData>
